--- a/04_Bug_Reports/Bug_Log_Summary.xlsx
+++ b/04_Bug_Reports/Bug_Log_Summary.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\ktpm\manual_testing\04_Bug_Reports\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA398983-0A2D-4DA6-B1F9-844A17770185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,15 +24,286 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="65">
+  <si>
+    <t>Bug ID</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Chrome, Windows</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Tóm tắt (Summary)</t>
+  </si>
+  <si>
+    <t>BUG_CART_004</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>BUG_CART_016</t>
+  </si>
+  <si>
+    <t>BUG_CART_005</t>
+  </si>
+  <si>
+    <t>Major</t>
+  </si>
+  <si>
+    <t>BUG_CART_012</t>
+  </si>
+  <si>
+    <t>BUG_CART_017</t>
+  </si>
+  <si>
+    <t>BUG_CART_006</t>
+  </si>
+  <si>
+    <t>Minor</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>BUG_CART_007</t>
+  </si>
+  <si>
+    <t>Các bước tái hiện (Steps to Reproduce)</t>
+  </si>
+  <si>
+    <t>Kết quả mong đợi (Expected)</t>
+  </si>
+  <si>
+    <t>Kết quả thực tế (Actual)</t>
+  </si>
+  <si>
+    <t>Mức độ nghiêm trọng (Severity)</t>
+  </si>
+  <si>
+    <t>Độ ưu tiên (Priority)</t>
+  </si>
+  <si>
+    <t>Môi trường (Environment)</t>
+  </si>
+  <si>
+    <t>Cho phép thêm SP với số lượng âm vào giỏ</t>
+  </si>
+  <si>
+    <t>Hệ thống báo lỗi, không cho phép thêm số âm.</t>
+  </si>
+  <si>
+    <t>SP vẫn được thêm thành công với số lượng -5.</t>
+  </si>
+  <si>
+    <t>Thanh toán thành công khi giỏ hàng trống</t>
+  </si>
+  <si>
+    <t>Hệ thống chặn truy cập và báo giỏ hàng trống.</t>
+  </si>
+  <si>
+    <t>Vẫn vào được trang Checkout và thực hiện thanh toán.</t>
+  </si>
+  <si>
+    <t>Nhập 0 vẫn add vào giỏ hàng được</t>
+  </si>
+  <si>
+    <t>Hệ thống yêu cầu số lượng phải &gt; 0.</t>
+  </si>
+  <si>
+    <t>SP hiển thị trong giỏ với Quantity = 0.</t>
+  </si>
+  <si>
+    <t>Không thể sửa số lượng tại trang Giỏ hàng</t>
+  </si>
+  <si>
+    <t>Người dùng có thể chỉnh sửa và cập nhật lại tiền.</t>
+  </si>
+  <si>
+    <t>Ô Quantity bị khóa, không thể thay đổi giá trị.</t>
+  </si>
+  <si>
+    <t>Nhập số thập phân không phản hồi</t>
+  </si>
+  <si>
+    <t>Báo lỗi định dạng số hoặc tự động làm tròn.</t>
+  </si>
+  <si>
+    <t>Không báo lỗi và cũng không thêm được SP vào giỏ.</t>
+  </si>
+  <si>
+    <t>Lỗi bảo mật XSS tại ô tìm kiếm</t>
+  </si>
+  <si>
+    <t>Hệ thống lọc mã độc, chỉ hiển thị văn bản thuần.</t>
+  </si>
+  <si>
+    <t>Trình duyệt thực thi script và hiện popup alert.</t>
+  </si>
+  <si>
+    <t>Nhập 9999 vẫn add cart được thành công</t>
+  </si>
+  <si>
+    <t>Hệ thống cảnh báo giới hạn đặt hàng tối đa.</t>
+  </si>
+  <si>
+    <t>Vẫn add thành công 9999 sản phẩm vào giỏ.</t>
+  </si>
+  <si>
+    <t>Không báo lỗi khi nhập chữ vào ô số lượng</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo yêu cầu nhập định dạng số.</t>
+  </si>
+  <si>
+    <t>Không nhập được chữ nhưng cũng không báo lỗi.</t>
+  </si>
+  <si>
+    <t>Ảnh sản phẩm trong giỏ hàng bị vỡ layout</t>
+  </si>
+  <si>
+    <t>Ảnh hiển thị đúng tỉ lệ, rõ nét.</t>
+  </si>
+  <si>
+    <t>Ảnh bị kéo giãn, méo hình so với thực tế.</t>
+  </si>
+  <si>
+    <t>Tìm kiếm ký tự đặc biệt gây lỗi giao diện</t>
+  </si>
+  <si>
+    <t>Thông báo không tìm thấy kết quả một cách rõ ràng.</t>
+  </si>
+  <si>
+    <t>Layout trang Products bị lệch, vỡ khung hiển thị.</t>
+  </si>
+  <si>
+    <t>1. Để giỏ hàng trống.
+2. Truy cập URL /checkout.
+3. Nhấn thanh toán.</t>
+  </si>
+  <si>
+    <t>1. Vào trang chi tiết SP.
+2. Nhập "-5" vào ô Quantity.
+3. Nhấn "Add to cart".</t>
+  </si>
+  <si>
+    <t>1. Nhập "0" vào ô Quantity.
+2. Nhấn "Add to cart".</t>
+  </si>
+  <si>
+    <t>1. Vào trang Giỏ hàng.
+2. Thử sửa số lượng trực tiếp tại ô Quantity.</t>
+  </si>
+  <si>
+    <t>1. Nhập "1.5" vào ô Quantity.
+2. Nhấn "Add to cart".</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Nhập </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;script&gt;alert(1)&lt;/script&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> vào ô Search.
+2. Nhấn Search.</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Nhập "9999" vào ô Quantity.
+2. Nhấn "Add to cart".</t>
+  </si>
+  <si>
+    <t>1. Nhập "abc" vào ô Quantity.
+2. Nhấn "Add to cart".</t>
+  </si>
+  <si>
+    <t>1. Thêm SP vào giỏ.
+2. Xem lại ảnh SP tại trang Cart.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Nhập </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>@#$%^&amp;*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> vào ô Search.
+2. Nhấn Search.</t>
+    </r>
+  </si>
+  <si>
+    <t>BUG_PRODUCT_011</t>
+  </si>
+  <si>
+    <t>BUG_PRODUCT_018</t>
+  </si>
+  <si>
+    <t>BUG_PRODUCT_003</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF444746"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +314,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -45,12 +322,80 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +675,307 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="22.21875" customWidth="1"/>
+    <col min="2" max="2" width="34.6640625" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" customWidth="1"/>
+    <col min="4" max="4" width="26.88671875" customWidth="1"/>
+    <col min="5" max="5" width="20.5546875" customWidth="1"/>
+    <col min="6" max="6" width="23.88671875" customWidth="1"/>
+    <col min="7" max="7" width="23" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="56.4" customHeight="1" thickBot="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="79.2" customHeight="1" thickBot="1">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="73.8" customHeight="1" thickBot="1">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="62.4" customHeight="1" thickBot="1">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="54.6" customHeight="1" thickBot="1">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="42" thickBot="1">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="65.400000000000006" customHeight="1" thickBot="1">
+      <c r="A7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="54" customHeight="1" thickBot="1">
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="61.2" customHeight="1" thickBot="1">
+      <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="53.4" customHeight="1" thickBot="1">
+      <c r="A10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="6" customFormat="1" ht="41.4">
+      <c r="A11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/04_Bug_Reports/Bug_Log_Summary.xlsx
+++ b/04_Bug_Reports/Bug_Log_Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\ktpm\manual_testing\04_Bug_Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA398983-0A2D-4DA6-B1F9-844A17770185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74368EE4-7F7F-431F-A326-FA3B116B78F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="70">
   <si>
     <t>Bug ID</t>
   </si>
@@ -273,12 +273,28 @@
   <si>
     <t>BUG_PRODUCT_003</t>
   </si>
+  <si>
+    <t>BUG_PRODUCT_021</t>
+  </si>
+  <si>
+    <t>Không có chức năng lọc sản phẩm theo giá</t>
+  </si>
+  <si>
+    <t>1. Truy cập trang Products
+2. Tìm chức năng Filter Price</t>
+  </si>
+  <si>
+    <t>Có bộ lọc giá để lọc sản phẩm</t>
+  </si>
+  <si>
+    <t>Không tồn tại chức năng filter</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -305,6 +321,12 @@
       <name val="Google Sans Text"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -314,7 +336,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -374,11 +396,63 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -396,6 +470,27 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -676,14 +771,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="22.21875" customWidth="1"/>
-    <col min="2" max="2" width="34.6640625" customWidth="1"/>
+    <col min="2" max="2" width="42.6640625" customWidth="1"/>
     <col min="3" max="3" width="25.6640625" customWidth="1"/>
-    <col min="4" max="4" width="26.88671875" customWidth="1"/>
-    <col min="5" max="5" width="20.5546875" customWidth="1"/>
+    <col min="4" max="4" width="28.77734375" customWidth="1"/>
+    <col min="5" max="5" width="28.44140625" customWidth="1"/>
     <col min="6" max="6" width="23.88671875" customWidth="1"/>
     <col min="7" max="7" width="23" customWidth="1"/>
     <col min="8" max="8" width="23.6640625" customWidth="1"/>
@@ -949,7 +1044,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="6" customFormat="1" ht="41.4">
+    <row r="11" spans="1:8" s="6" customFormat="1" ht="42" thickBot="1">
       <c r="A11" s="4" t="s">
         <v>64</v>
       </c>
@@ -968,10 +1063,36 @@
       <c r="F11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="H11" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="43.2" customHeight="1">
+      <c r="A12" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="8" t="s">
         <v>2</v>
       </c>
     </row>

--- a/04_Bug_Reports/Bug_Log_Summary.xlsx
+++ b/04_Bug_Reports/Bug_Log_Summary.xlsx
@@ -1,32 +1,241 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Sửa lỗi trang web automationexe" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="68">
+  <si>
+    <t>Bug ID</t>
+  </si>
+  <si>
+    <t>Tóm tắt (Summary)</t>
+  </si>
+  <si>
+    <t>Các bước tái hiện (Steps to Reproduce)</t>
+  </si>
+  <si>
+    <t>Kết quả mong đợi (Expected)</t>
+  </si>
+  <si>
+    <t>Kết quả thực tế (Actual)</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>BUG_AUTH_001</t>
+  </si>
+  <si>
+    <t>Mật khẩu 1 ký tự vẫn đăng ký được</t>
+  </si>
+  <si>
+    <t>1. Trang Signup. 2. Nhập Email/Name. 3. Nhập Pass "1". 4. Nhấn Create.</t>
+  </si>
+  <si>
+    <t>Báo lỗi mật khẩu phải $\ge$ 8 ký tự.</t>
+  </si>
+  <si>
+    <t>Đăng ký thành công với 1 ký tự.</t>
+  </si>
+  <si>
+    <t>Major</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>BUG_PROD_001</t>
+  </si>
+  <si>
+    <t>Lỗ hổng XSS tại ô Search</t>
+  </si>
+  <si>
+    <t>1. Trang Products. 2. Nhập &lt;script&gt;alert(1)&lt;/script&gt;. 3. Nhấn Search.</t>
+  </si>
+  <si>
+    <t>Chặn mã độc, hiển thị không tìm thấy kết quả.</t>
+  </si>
+  <si>
+    <t>Trình duyệt thực thi mã, hiện popup Alert.</t>
+  </si>
+  <si>
+    <t>BUG_CART_001</t>
+  </si>
+  <si>
+    <t>Cho phép thêm số lượng âm (-5)</t>
+  </si>
+  <si>
+    <t>1. Trang chi tiết SP. 2. Nhập "-5" vào Quantity. 3. Add to cart.</t>
+  </si>
+  <si>
+    <t>Báo lỗi hoặc tự điều chỉnh về 1.</t>
+  </si>
+  <si>
+    <t>Giỏ hàng hiển thị số lượng -5.</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>BUG_CART_002</t>
+  </si>
+  <si>
+    <t>Cho phép thêm số lượng bằng 0</t>
+  </si>
+  <si>
+    <t>1. Trang chi tiết SP. 2. Nhập "0" vào Quantity. 3. Add to cart.</t>
+  </si>
+  <si>
+    <t>Không cho phép thêm 0 sản phẩm.</t>
+  </si>
+  <si>
+    <t>Hiện "Added!" thành công với số lượng 0.</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>BUG_CART_003</t>
+  </si>
+  <si>
+    <t>Không chặn số lượng cực lớn (9999)</t>
+  </si>
+  <si>
+    <t>1. Trang chi tiết SP. 2. Nhập "9999" vào Quantity. 3. Add to cart.</t>
+  </si>
+  <si>
+    <t>Cảnh báo vượt quá giới hạn đặt hàng.</t>
+  </si>
+  <si>
+    <t>Cho phép thêm 9999 SP vào giỏ.</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>BUG_CART_004</t>
+  </si>
+  <si>
+    <t>Ô số lượng trong giỏ bị khóa (Read-only)</t>
+  </si>
+  <si>
+    <t>1. Thêm SP vào giỏ. 2. Vào trang Cart. 3. Sửa số lượng tại ô Quantity.</t>
+  </si>
+  <si>
+    <t>Người dùng có thể chỉnh sửa số lượng.</t>
+  </si>
+  <si>
+    <t>Ô nhập bị khóa, không thể tương tác.</t>
+  </si>
+  <si>
+    <t>BUG_CART_005</t>
+  </si>
+  <si>
+    <t>Không xử lý khi nhập số thập phân</t>
+  </si>
+  <si>
+    <t>1. Trang chi tiết SP. 2. Nhập "1.5" vào Quantity. 3. Add to cart.</t>
+  </si>
+  <si>
+    <t>Báo lỗi định dạng hoặc tự làm tròn.</t>
+  </si>
+  <si>
+    <t>Không thêm được SP, không báo lỗi.</t>
+  </si>
+  <si>
+    <t>Minor</t>
+  </si>
+  <si>
+    <t>BUG_PROD_002</t>
+  </si>
+  <si>
+    <t>Ảnh sản phẩm trong giỏ bị vỡ layout</t>
+  </si>
+  <si>
+    <t>1. Thêm SP vào giỏ. 2. Vào trang Cart và xem ảnh SP.</t>
+  </si>
+  <si>
+    <t>Ảnh hiển thị đúng tỷ lệ, sắc nét.</t>
+  </si>
+  <si>
+    <t>Ảnh bị kéo giãn, vỡ khung hình.</t>
+  </si>
+  <si>
+    <t>BUG_CHKT_001</t>
+  </si>
+  <si>
+    <t>Truy cập Checkout khi giỏ hàng trống</t>
+  </si>
+  <si>
+    <t>1. Đảm bảo giỏ trống. 2. Nhập URL /checkout vào trình duyệt.</t>
+  </si>
+  <si>
+    <t>Redirect về trang Cart, báo giỏ trống.</t>
+  </si>
+  <si>
+    <t>Truy cập thành công trang thanh toán.</t>
+  </si>
+  <si>
+    <t>BUG_CHKT_002</t>
+  </si>
+  <si>
+    <t>Chấp nhận thẻ tín dụng đã hết hạn</t>
+  </si>
+  <si>
+    <t>1. Checkout. 2. Nhập thẻ có năm hết hạn là "2020". 3. Xác nhận.</t>
+  </si>
+  <si>
+    <t>Từ chối giao dịch do thẻ hết hạn.</t>
+  </si>
+  <si>
+    <t>Đặt hàng thành công (Order Placed).</t>
+  </si>
+  <si>
+    <t>BUG_CHKT_003</t>
+  </si>
+  <si>
+    <t>Lỗi Double Click tạo đơn trùng</t>
+  </si>
+  <si>
+    <t>1. Trang thanh toán. 2. Nhấn nhanh 2 lần nút "Pay and Confirm".</t>
+  </si>
+  <si>
+    <t>Chỉ xử lý 1 lần, tạo 1 đơn hàng.</t>
+  </si>
+  <si>
+    <t>Tạo ra 2 đơn hàng giống hệt nhau.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1F1F1F"/>
+      <name val="&quot;Google Sans Text&quot;"/>
+    </font>
+    <font>
+      <color rgb="FF1F1F1F"/>
+      <name val="&quot;Google Sans Text&quot;"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,151 +243,92 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Sheets">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4285F4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="EA4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="FBBC04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="34A853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="FF6D01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="1155CC"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="1155CC"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -319,21 +469,298 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="16.25"/>
+    <col customWidth="1" min="3" max="3" width="20.38"/>
+    <col customWidth="1" min="4" max="4" width="16.13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>